--- a/docs/design/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
@@ -6239,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ57"/>
+  <dimension ref="A1:BQ58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9371,7 +9371,7 @@
       <c r="BP26" s="10" t="n"/>
       <c r="BQ26" s="11" t="n"/>
     </row>
-    <row r="27" ht="144" customHeight="1">
+    <row r="27" ht="192" customHeight="1">
       <c r="A27" s="44" t="n">
         <v>14</v>
       </c>
@@ -9384,7 +9384,7 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="46" t="inlineStr">
         <is>
-          <t>購読種別・支払区分プルダウン</t>
+          <t>購読種別・支払い方法プルダウン</t>
         </is>
       </c>
       <c r="F27" s="10" t="n"/>
@@ -9435,7 +9435,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>支払区分プルダウンを開き、選択肢を確認する</t>
+            <t>支払い方法プルダウンを開き、選択肢を確認する</t>
           </r>
         </is>
       </c>
@@ -9478,7 +9478,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>支払区分に「毎月」「隔月」「3ヶ月」「半年」「年払い」が表示されること</t>
+            <t>支払い方法に m_code SHIHARAI_HOHO の「口座引落」「現金集金」「振込集金」「JA施設等」「給与天引き」「クレジットカード」「その他」が表示されること</t>
           </r>
         </is>
       </c>
@@ -9800,7 +9800,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Tabキーで適用日 → 帳票種別 → 販売店／管理支店 → 購読種別 → 支払区分 → ボタンの順に移動できること
+            <t xml:space="preserve">・Tabキーで適用日 → 帳票種別 → 販売店／管理支店 → 購読種別 → 支払い方法 → ボタンの順に移動できること
 </t>
           </r>
           <r>
@@ -11879,7 +11879,7 @@
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>支払区分フィルタ</t>
+          <t>支払い方法フィルタ</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -11914,7 +11914,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>支払区分=毎月（1）を選択して「レポートプレビュー」を実行する</t>
+            <t>支払い方法=口座引落（1）を選択して「レポートプレビュー」を実行する</t>
           </r>
         </is>
       </c>
@@ -11940,7 +11940,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>購読料支払サイクルが毎月（dokusyaryo_shiharai_cycle=1）の購読者のみが表示されること</t>
+            <t>支払方法が口座引落（shiharai_hoho=1）の購読者のみが表示されること</t>
           </r>
         </is>
       </c>
@@ -13842,7 +13842,12 @@
       <c r="BH57" s="45" t="inlineStr"/>
       <c r="BI57" s="10" t="n"/>
       <c r="BJ57" s="11" t="n"/>
-      <c r="BK57" s="46" t="inlineStr"/>
+      <c r="BK57" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL57" s="10" t="n"/>
       <c r="BM57" s="10" t="n"/>
       <c r="BN57" s="10" t="n"/>
@@ -13850,11 +13855,395 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
+    <row r="58" ht="450" customHeight="1">
+      <c r="A58" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-042</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>支店による絞込み（管理支店別のみ・任意条件）</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="11" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100・`report.export_meibo` 権限あり）
+・管理支店 A（kanri_shiten_id=10）配下に 支店 X（shiten_id=21）／支店 Y（shiten_id=22）が存在
+・管理支店 B（kanri_shiten_id=11）配下に 支店 Z（shiten_id=31）が存在
+・適用日時点で有効な購読者：支店 X に 3件、支店 Y に 2件、支店未設定（shiten_id が NULL）が 1件（いずれも管理支店 A 配下）</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別に「販売店別購読者名簿」を選んだ状態で、支店の入力欄が表示されるか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別を「管理支店別購読者名簿」に切り替え、管理支店を未選択のまま支店の入力欄を操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">管理支店に A を選び、支店ドロップダウンを開いて候補を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店を選ばずに「レポートプレビュー」を押す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店に X のみを選んで「レポートプレビュー」を押す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店に X を選んだ状態のまま、管理支店を A から B に変更する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>管理支店 A ＋ 支店 X の条件で「レポートデータExcel出力」を押す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="11" t="n"/>
+      <c r="X58" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の入力欄は表示されないこと（販売店別の帳票には支店列が無いため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の入力欄は表示されるが非活性で、「先に管理支店を選択してください」の案内が出ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店 X と 支店 Y のみが候補に出ること。管理支店 B 配下の 支店 Z は出ないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店は任意条件のため検証エラーにならず、管理支店 A 配下の全 6件（支店未設定の1件を含む）が出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店 X の 3件のみが出力されること。**支店未設定の1件は含まれない**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の選択が自動で解除され（空になり）、候補が 支店 Z に入れ替わること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビューと同じ 3件が Excel に出力され、`t_file_download` に登録されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・支店 = 配達担当支店（`t_dokusya_rireki.shiten_id`）。銀行支店（`bank_shiten_id`）ではない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`shiten_id` は購読者登録で任意項目のため NULL があり得る。**電子版連携で取り込んだ購読者は常に NULL**（電子版に配達担当支店の概念が無いため）。支店を1件でも選ぶと NULL の購読者は IN 比較が NULL となり対象外になる（ステップ5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・一時期この支店条件を必須にしていたが、それだと NULL の購読者がどう操作しても名簿へ出せなかった（「全て」を選んでも実在する支店IDを列挙するだけで NULL は拾えない）ため任意へ戻した（顧客要件 2026-08 改訂）。ステップ4がその回帰確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・管理支店を変えたときに支店の選択を持ち越さないのは、配下に無い支店で絞ったままだと結果0件になった理由が画面から読み取れないため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・販売店別で支店条件を出さないのは、帳票に支店列が無く絞込みの理由が紙面から読めないため。API 側も `report_type=hanbaiten` のときは `shiten_ids` を無視する</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+      <c r="AE58" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF58" s="11" t="n"/>
+      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="11" t="n"/>
+      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AK58" s="10" t="n"/>
+      <c r="AL58" s="11" t="n"/>
+      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AN58" s="10" t="n"/>
+      <c r="AO58" s="11" t="n"/>
+      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AQ58" s="10" t="n"/>
+      <c r="AR58" s="11" t="n"/>
+      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AT58" s="10" t="n"/>
+      <c r="AU58" s="11" t="n"/>
+      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AW58" s="10" t="n"/>
+      <c r="AX58" s="11" t="n"/>
+      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AZ58" s="10" t="n"/>
+      <c r="BA58" s="11" t="n"/>
+      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BC58" s="10" t="n"/>
+      <c r="BD58" s="11" t="n"/>
+      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BF58" s="10" t="n"/>
+      <c r="BG58" s="11" t="n"/>
+      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BI58" s="10" t="n"/>
+      <c r="BJ58" s="11" t="n"/>
+      <c r="BK58" s="46" t="inlineStr"/>
+      <c r="BL58" s="10" t="n"/>
+      <c r="BM58" s="10" t="n"/>
+      <c r="BN58" s="10" t="n"/>
+      <c r="BO58" s="10" t="n"/>
+      <c r="BP58" s="10" t="n"/>
+      <c r="BQ58" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="768">
+  <mergeCells count="785">
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
+    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="E52:I52"/>
@@ -13892,6 +14281,7 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
@@ -13932,6 +14322,7 @@
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="AY57:BA57"/>
+    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
@@ -14005,6 +14396,7 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
+    <mergeCell ref="AE58:AF58"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
@@ -14051,6 +14443,7 @@
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="AV34:AX34"/>
+    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
@@ -14092,6 +14485,7 @@
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
+    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14181,7 +14575,9 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="A30:BQ30"/>
+    <mergeCell ref="BB58:BD58"/>
     <mergeCell ref="J47:P47"/>
+    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
@@ -14240,6 +14636,7 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="Q6:S6"/>
     <mergeCell ref="BK34:BQ34"/>
+    <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
@@ -14264,6 +14661,7 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
+    <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
@@ -14273,6 +14671,7 @@
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="AE45:AF45"/>
+    <mergeCell ref="X58:AD58"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
@@ -14362,6 +14761,7 @@
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="Q58:W58"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14410,6 +14810,7 @@
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -14424,6 +14825,7 @@
     <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="BE45:BG45"/>
+    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14574,6 +14976,7 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
     <mergeCell ref="AJ42:AL42"/>
+    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
@@ -14587,6 +14990,7 @@
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="J56:P56"/>
+    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
@@ -14620,15 +15024,16 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
+    <mergeCell ref="B58:D58"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/design/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
+++ b/docs/design/ACSMS-SCR-026/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者名簿出力画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1363,20 +1363,78 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分補完：カテゴリ6を新設し2件追加（TC-043〜044）。043＝集計対象の購読種別を帳票種別ごとに分けたこと（顧客要件2026-08 / #56597・API設計書 v1.3）。販売店別＝紙版のみ、管理支店別＝紙版(無条件)＋併読(有料)＋電子版(有料かつ承認済)。有料判定は等値(=1)でNULLを通さないこと、併読の部数は入力値のまま扱うこと(1に丸めない)も確認する。044＝販売店候補から電子版ダミー販売店(9999999999)を除外したこと(`dummy=exclude`)。あわせて集計表を実数に合わせた（41→44。既存の042 がカテゴリ5配下に紛れて未計上だった）</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6239,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ58"/>
+  <dimension ref="A1:BQ61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13855,382 +13913,74 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="450" customHeight="1">
-      <c r="A58" s="44" t="n">
-        <v>42</v>
-      </c>
-      <c r="B58" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-026-042</t>
-        </is>
-      </c>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>カテゴリ6: 集計対象・販売店候補（Scope / Hanbaiten Options）</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
-      <c r="D58" s="11" t="n"/>
-      <c r="E58" s="46" t="inlineStr">
-        <is>
-          <t>支店による絞込み（管理支店別のみ・任意条件）</t>
-        </is>
-      </c>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="11" t="n"/>
-      <c r="J58" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100・`report.export_meibo` 権限あり）
-・管理支店 A（kanri_shiten_id=10）配下に 支店 X（shiten_id=21）／支店 Y（shiten_id=22）が存在
-・管理支店 B（kanri_shiten_id=11）配下に 支店 Z（shiten_id=31）が存在
-・適用日時点で有効な購読者：支店 X に 3件、支店 Y に 2件、支店未設定（shiten_id が NULL）が 1件（いずれも管理支店 A 配下）</t>
-        </is>
-      </c>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
       <c r="K58" s="10" t="n"/>
       <c r="L58" s="10" t="n"/>
       <c r="M58" s="10" t="n"/>
       <c r="N58" s="10" t="n"/>
       <c r="O58" s="10" t="n"/>
-      <c r="P58" s="11" t="n"/>
-      <c r="Q58" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">帳票種別に「販売店別購読者名簿」を選んだ状態で、支店の入力欄が表示されるか確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">帳票種別を「管理支店別購読者名簿」に切り替え、管理支店を未選択のまま支店の入力欄を操作する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">管理支店に A を選び、支店ドロップダウンを開いて候補を確認する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店を選ばずに「レポートプレビュー」を押す
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店に X のみを選んで「レポートプレビュー」を押す
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店に X を選んだ状態のまま、管理支店を A から B に変更する
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ7：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>管理支店 A ＋ 支店 X の条件で「レポートデータExcel出力」を押す</t>
-          </r>
-        </is>
-      </c>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
       <c r="R58" s="10" t="n"/>
       <c r="S58" s="10" t="n"/>
       <c r="T58" s="10" t="n"/>
       <c r="U58" s="10" t="n"/>
       <c r="V58" s="10" t="n"/>
-      <c r="W58" s="11" t="n"/>
-      <c r="X58" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店の入力欄は表示されないこと（販売店別の帳票には支店列が無いため）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店の入力欄は表示されるが非活性で、「先に管理支店を選択してください」の案内が出ること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店 X と 支店 Y のみが候補に出ること。管理支店 B 配下の 支店 Z は出ないこと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店は任意条件のため検証エラーにならず、管理支店 A 配下の全 6件（支店未設定の1件を含む）が出力されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ5：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店 X の 3件のみが出力されること。**支店未設定の1件は含まれない**こと
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ6：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">支店の選択が自動で解除され（空になり）、候補が 支店 Z に入れ替わること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ7：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">プレビューと同じ 3件が Excel に出力され、`t_file_download` に登録されること
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・支店 = 配達担当支店（`t_dokusya_rireki.shiten_id`）。銀行支店（`bank_shiten_id`）ではない
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・`shiten_id` は購読者登録で任意項目のため NULL があり得る。**電子版連携で取り込んだ購読者は常に NULL**（電子版に配達担当支店の概念が無いため）。支店を1件でも選ぶと NULL の購読者は IN 比較が NULL となり対象外になる（ステップ5）
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・一時期この支店条件を必須にしていたが、それだと NULL の購読者がどう操作しても名簿へ出せなかった（「全て」を選んでも実在する支店IDを列挙するだけで NULL は拾えない）ため任意へ戻した（顧客要件 2026-08 改訂）。ステップ4がその回帰確認
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・管理支店を変えたときに支店の選択を持ち越さないのは、配下に無い支店で絞ったままだと結果0件になった理由が画面から読み取れないため
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・販売店別で支店条件を出さないのは、帳票に支店列が無く絞込みの理由が紙面から読めないため。API 側も `report_type=hanbaiten` のときは `shiten_ids` を無視する</t>
-          </r>
-        </is>
-      </c>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
       <c r="Y58" s="10" t="n"/>
       <c r="Z58" s="10" t="n"/>
       <c r="AA58" s="10" t="n"/>
       <c r="AB58" s="10" t="n"/>
       <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="11" t="n"/>
-      <c r="AE58" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF58" s="11" t="n"/>
-      <c r="AG58" s="45" t="inlineStr"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
       <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="11" t="n"/>
-      <c r="AJ58" s="45" t="inlineStr"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
       <c r="AK58" s="10" t="n"/>
-      <c r="AL58" s="11" t="n"/>
-      <c r="AM58" s="45" t="inlineStr"/>
+      <c r="AL58" s="10" t="n"/>
+      <c r="AM58" s="10" t="n"/>
       <c r="AN58" s="10" t="n"/>
-      <c r="AO58" s="11" t="n"/>
-      <c r="AP58" s="45" t="inlineStr"/>
+      <c r="AO58" s="10" t="n"/>
+      <c r="AP58" s="10" t="n"/>
       <c r="AQ58" s="10" t="n"/>
-      <c r="AR58" s="11" t="n"/>
-      <c r="AS58" s="45" t="inlineStr"/>
+      <c r="AR58" s="10" t="n"/>
+      <c r="AS58" s="10" t="n"/>
       <c r="AT58" s="10" t="n"/>
-      <c r="AU58" s="11" t="n"/>
-      <c r="AV58" s="45" t="inlineStr"/>
+      <c r="AU58" s="10" t="n"/>
+      <c r="AV58" s="10" t="n"/>
       <c r="AW58" s="10" t="n"/>
-      <c r="AX58" s="11" t="n"/>
-      <c r="AY58" s="45" t="inlineStr"/>
+      <c r="AX58" s="10" t="n"/>
+      <c r="AY58" s="10" t="n"/>
       <c r="AZ58" s="10" t="n"/>
-      <c r="BA58" s="11" t="n"/>
-      <c r="BB58" s="45" t="inlineStr"/>
+      <c r="BA58" s="10" t="n"/>
+      <c r="BB58" s="10" t="n"/>
       <c r="BC58" s="10" t="n"/>
-      <c r="BD58" s="11" t="n"/>
-      <c r="BE58" s="45" t="inlineStr"/>
+      <c r="BD58" s="10" t="n"/>
+      <c r="BE58" s="10" t="n"/>
       <c r="BF58" s="10" t="n"/>
-      <c r="BG58" s="11" t="n"/>
-      <c r="BH58" s="45" t="inlineStr"/>
+      <c r="BG58" s="10" t="n"/>
+      <c r="BH58" s="10" t="n"/>
       <c r="BI58" s="10" t="n"/>
-      <c r="BJ58" s="11" t="n"/>
-      <c r="BK58" s="46" t="inlineStr"/>
+      <c r="BJ58" s="10" t="n"/>
+      <c r="BK58" s="10" t="n"/>
       <c r="BL58" s="10" t="n"/>
       <c r="BM58" s="10" t="n"/>
       <c r="BN58" s="10" t="n"/>
@@ -14238,20 +13988,954 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
+    <row r="59" ht="450" customHeight="1">
+      <c r="A59" s="44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-042</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>支店による絞込み（管理支店別のみ・任意条件）</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100・`report.export_meibo` 権限あり）
+・管理支店 A（kanri_shiten_id=10）配下に 支店 X（shiten_id=21）／支店 Y（shiten_id=22）が存在
+・管理支店 B（kanri_shiten_id=11）配下に 支店 Z（shiten_id=31）が存在
+・適用日時点で有効な購読者：支店 X に 3件、支店 Y に 2件、支店未設定（shiten_id が NULL）が 1件（いずれも管理支店 A 配下）</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="10" t="n"/>
+      <c r="M59" s="10" t="n"/>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別に「販売店別購読者名簿」を選んだ状態で、支店の入力欄が表示されるか確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別を「管理支店別購読者名簿」に切り替え、管理支店を未選択のまま支店の入力欄を操作する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">管理支店に A を選び、支店ドロップダウンを開いて候補を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店を選ばずに「レポートプレビュー」を押す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店に X のみを選んで「レポートプレビュー」を押す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店に X を選んだ状態のまま、管理支店を A から B に変更する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>管理支店 A ＋ 支店 X の条件で「レポートデータExcel出力」を押す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="10" t="n"/>
+      <c r="T59" s="10" t="n"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="11" t="n"/>
+      <c r="X59" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の入力欄は表示されないこと（販売店別の帳票には支店列が無いため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の入力欄は表示されるが非活性で、「先に管理支店を選択してください」の案内が出ること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店 X と 支店 Y のみが候補に出ること。管理支店 B 配下の 支店 Z は出ないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店は任意条件のため検証エラーにならず、管理支店 A 配下の全 6件（支店未設定の1件を含む）が出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店 X の 3件のみが出力されること。**支店未設定の1件は含まれない**こと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">支店の選択が自動で解除され（空になり）、候補が 支店 Z に入れ替わること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">プレビューと同じ 3件が Excel に出力され、`t_file_download` に登録されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・支店 = 配達担当支店（`t_dokusya_rireki.shiten_id`）。銀行支店（`bank_shiten_id`）ではない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`shiten_id` は購読者登録で任意項目のため NULL があり得る。**電子版連携で取り込んだ購読者は常に NULL**（電子版に配達担当支店の概念が無いため）。支店を1件でも選ぶと NULL の購読者は IN 比較が NULL となり対象外になる（ステップ5）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・一時期この支店条件を必須にしていたが、それだと NULL の購読者がどう操作しても名簿へ出せなかった（「全て」を選んでも実在する支店IDを列挙するだけで NULL は拾えない）ため任意へ戻した（顧客要件 2026-08 改訂）。ステップ4がその回帰確認
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・管理支店を変えたときに支店の選択を持ち越さないのは、配下に無い支店で絞ったままだと結果0件になった理由が画面から読み取れないため
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・販売店別で支店条件を出さないのは、帳票に支店列が無く絞込みの理由が紙面から読めないため。API 側も `report_type=hanbaiten` のときは `shiten_ids` を無視する</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y59" s="10" t="n"/>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+      <c r="AE59" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF59" s="11" t="n"/>
+      <c r="AG59" s="45" t="inlineStr"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="11" t="n"/>
+      <c r="AJ59" s="45" t="inlineStr"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="11" t="n"/>
+      <c r="AM59" s="45" t="inlineStr"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="11" t="n"/>
+      <c r="AP59" s="45" t="inlineStr"/>
+      <c r="AQ59" s="10" t="n"/>
+      <c r="AR59" s="11" t="n"/>
+      <c r="AS59" s="45" t="inlineStr"/>
+      <c r="AT59" s="10" t="n"/>
+      <c r="AU59" s="11" t="n"/>
+      <c r="AV59" s="45" t="inlineStr"/>
+      <c r="AW59" s="10" t="n"/>
+      <c r="AX59" s="11" t="n"/>
+      <c r="AY59" s="45" t="inlineStr"/>
+      <c r="AZ59" s="10" t="n"/>
+      <c r="BA59" s="11" t="n"/>
+      <c r="BB59" s="45" t="inlineStr"/>
+      <c r="BC59" s="10" t="n"/>
+      <c r="BD59" s="11" t="n"/>
+      <c r="BE59" s="45" t="inlineStr"/>
+      <c r="BF59" s="10" t="n"/>
+      <c r="BG59" s="11" t="n"/>
+      <c r="BH59" s="45" t="inlineStr"/>
+      <c r="BI59" s="10" t="n"/>
+      <c r="BJ59" s="11" t="n"/>
+      <c r="BK59" s="46" t="inlineStr"/>
+      <c r="BL59" s="10" t="n"/>
+      <c r="BM59" s="10" t="n"/>
+      <c r="BN59" s="10" t="n"/>
+      <c r="BO59" s="10" t="n"/>
+      <c r="BP59" s="10" t="n"/>
+      <c r="BQ59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="450" customHeight="1">
+      <c r="A60" s="44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-043</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>集計対象の購読種別が帳票種別ごとに分かれること（#56597）</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`report.export_meibo` 権限あり）
+・同一の管理支店・実在販売店の配下に、出力対象期間で購読中の購読者が以下のとおり存在すること
+・(a) 紙版（dokusya_shubetsu=1）2件
+・(b) 併読（3）・有料（denshi_dokusya_shubetsu=1）1件
+・(c) 併読（3）・無料（denshi_dokusya_shubetsu=0）1件
+・(d) 電子版（2）・有料・承認済（denshi_shonin_status=1）1件
+・(e) 電子版（2）・有料・未承認 1件
+・(f) 電子版（2）・無料・承認済 1件
+・(b) の購読部数は 2 部とすること</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別＝**販売店別**で出力し、名簿に載る購読者を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別＝**管理支店別**で出力し、名簿に載る購読者を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">管理支店別の出力で (b) 併読の部数を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>両帳票種別の合計部数を確認する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+      <c r="X60" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**(a) 紙版 2件のみ**が出力されること。併読（b)(c)・電子版（d)(e)(f) はいずれも対象外であること（販売店別は「紙を配達した対価」の単位で集計するため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**(a) 紙版2件 + (b) 併読・有料1件 + (d) 電子版・有料・承認済1件 の計4件**が出力されること。(c) 併読・無料、(e) 電子版・未承認、(f) 電子版・無料 は対象外であること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">併読の部数が**入力値のまま 2 部**として扱われること（1 に丸めないこと）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">それぞれの対象件数に対応した合計部数が出力されること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・従来は帳票種別に関わらず「併読を除外し、電子版は承認済のみ」という**共通条件**だったため、販売店別に電子版が混ざり、管理支店別からは対象にすべき併読が落ちていた（顧客要件2026-08 / #56597）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・有料判定は `denshi_dokusya_shubetsu = 1` の**等値**で行う。`&lt;&gt; 0` にすると NULL も通ってしまうため。`denshi_dokusya_shubetsu` は電子版・併読なら必ず値を持ち、NULL になるのは紙版だけという前提
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・承認済（`denshi_shonin_status = 1`）条件は**電子版のみ**に課す（併読については顧客要件に言及が無いため文面どおり）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・口座振替データ出力（SCR-020）・配達手数料支払情報出力（SCR-021）はさらに別の条件。帳票ごとに対象が異なるため流用しないこと</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+      <c r="AE60" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF60" s="11" t="n"/>
+      <c r="AG60" s="45" t="inlineStr"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="11" t="n"/>
+      <c r="AJ60" s="45" t="inlineStr"/>
+      <c r="AK60" s="10" t="n"/>
+      <c r="AL60" s="11" t="n"/>
+      <c r="AM60" s="45" t="inlineStr"/>
+      <c r="AN60" s="10" t="n"/>
+      <c r="AO60" s="11" t="n"/>
+      <c r="AP60" s="45" t="inlineStr"/>
+      <c r="AQ60" s="10" t="n"/>
+      <c r="AR60" s="11" t="n"/>
+      <c r="AS60" s="45" t="inlineStr"/>
+      <c r="AT60" s="10" t="n"/>
+      <c r="AU60" s="11" t="n"/>
+      <c r="AV60" s="45" t="inlineStr"/>
+      <c r="AW60" s="10" t="n"/>
+      <c r="AX60" s="11" t="n"/>
+      <c r="AY60" s="45" t="inlineStr"/>
+      <c r="AZ60" s="10" t="n"/>
+      <c r="BA60" s="11" t="n"/>
+      <c r="BB60" s="45" t="inlineStr"/>
+      <c r="BC60" s="10" t="n"/>
+      <c r="BD60" s="11" t="n"/>
+      <c r="BE60" s="45" t="inlineStr"/>
+      <c r="BF60" s="10" t="n"/>
+      <c r="BG60" s="11" t="n"/>
+      <c r="BH60" s="45" t="inlineStr"/>
+      <c r="BI60" s="10" t="n"/>
+      <c r="BJ60" s="11" t="n"/>
+      <c r="BK60" s="46" t="inlineStr"/>
+      <c r="BL60" s="10" t="n"/>
+      <c r="BM60" s="10" t="n"/>
+      <c r="BN60" s="10" t="n"/>
+      <c r="BO60" s="10" t="n"/>
+      <c r="BP60" s="10" t="n"/>
+      <c r="BQ60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="450" customHeight="1">
+      <c r="A61" s="44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-026-044</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="46" t="inlineStr">
+        <is>
+          <t>販売店候補から電子版ダミー販売店が除外されること（#56597）</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（`report.export_meibo` 権限あり）
+・自JAに電子版ダミー販売店（`hanbaiten_code = 9999999999`）が存在すること
+・ダミー販売店に電子版購読者が紐づいていること
+・実在の販売店も 2 件以上存在すること</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別＝販売店別を選択し、「販売店」プルダウンの候補を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`GET /api/v1/hanbaiten/dropdown` のリクエストパラメータを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別を管理支店別 → 販売店別 と切り替え、候補が取り直されることを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>DevTools からダミー販売店の `hanbaiten_id` を直接指定して出力APIを呼び出す</t>
+          </r>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+      <c r="X61" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">実在の販売店のみが候補に表示され、**ダミー販売店（9999999999）が候補に出ないこと**
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`dummy=exclude` が指定されていること
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">帳票種別の切り替えで候補集合が取り直されること（`dummy` の値が変わると候補が変わるため）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">0 件となること（ダミー配下は集計対象に入らないため、選べたとしても必ず0件になる）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・電子版ダミー販売店は「電子版読者を紐づける受け皿」であり実在の販売店ではない。`t_dokusya.hanbaiten_id` が NOT NULL のために用意している
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・同じ除外は増減連絡票（SCR-028）にも適用される
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・BE の `/hanbaiten/dropdown` は以前から `dummy=only|exclude` を受け付けていたが、共通部品 `BaseHanbaitenSelect` が prop を持たず SCR-011 だけが直接指定していた。本対応で両画面から `exclude` を渡すようにした</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+      <c r="AE61" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF61" s="11" t="n"/>
+      <c r="AG61" s="45" t="inlineStr"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="11" t="n"/>
+      <c r="AJ61" s="45" t="inlineStr"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="11" t="n"/>
+      <c r="AM61" s="45" t="inlineStr"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="11" t="n"/>
+      <c r="AP61" s="45" t="inlineStr"/>
+      <c r="AQ61" s="10" t="n"/>
+      <c r="AR61" s="11" t="n"/>
+      <c r="AS61" s="45" t="inlineStr"/>
+      <c r="AT61" s="10" t="n"/>
+      <c r="AU61" s="11" t="n"/>
+      <c r="AV61" s="45" t="inlineStr"/>
+      <c r="AW61" s="10" t="n"/>
+      <c r="AX61" s="11" t="n"/>
+      <c r="AY61" s="45" t="inlineStr"/>
+      <c r="AZ61" s="10" t="n"/>
+      <c r="BA61" s="11" t="n"/>
+      <c r="BB61" s="45" t="inlineStr"/>
+      <c r="BC61" s="10" t="n"/>
+      <c r="BD61" s="11" t="n"/>
+      <c r="BE61" s="45" t="inlineStr"/>
+      <c r="BF61" s="10" t="n"/>
+      <c r="BG61" s="11" t="n"/>
+      <c r="BH61" s="45" t="inlineStr"/>
+      <c r="BI61" s="10" t="n"/>
+      <c r="BJ61" s="11" t="n"/>
+      <c r="BK61" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL61" s="10" t="n"/>
+      <c r="BM61" s="10" t="n"/>
+      <c r="BN61" s="10" t="n"/>
+      <c r="BO61" s="10" t="n"/>
+      <c r="BP61" s="10" t="n"/>
+      <c r="BQ61" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="785">
+  <mergeCells count="820">
+    <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
+    <mergeCell ref="B60:D60"/>
     <mergeCell ref="Q27:W27"/>
     <mergeCell ref="AS46:AU46"/>
-    <mergeCell ref="BK58:BQ58"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="E52:I52"/>
     <mergeCell ref="AE41:AF41"/>
     <mergeCell ref="AV57:AX57"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
+    <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="BK16:BQ16"/>
@@ -14281,7 +14965,6 @@
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
-    <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="AM34:AO34"/>
     <mergeCell ref="AJ38:AL38"/>
@@ -14315,6 +14998,7 @@
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
     <mergeCell ref="BK53:BQ53"/>
+    <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
@@ -14322,16 +15006,18 @@
     <mergeCell ref="BE33:BG33"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="AY57:BA57"/>
-    <mergeCell ref="AM58:AO58"/>
     <mergeCell ref="BE41:BG41"/>
+    <mergeCell ref="Q59:W59"/>
     <mergeCell ref="J25:P25"/>
     <mergeCell ref="Q46:W46"/>
     <mergeCell ref="BH55:BJ55"/>
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="AG27:AI27"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="AM60:AO60"/>
     <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
+    <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="E33:I33"/>
     <mergeCell ref="Q48:W48"/>
@@ -14396,11 +15082,13 @@
     <mergeCell ref="BE56:BG56"/>
     <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
-    <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="X27:AD27"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="AY60:BA60"/>
+    <mergeCell ref="BB61:BD61"/>
     <mergeCell ref="AV15:AX15"/>
     <mergeCell ref="AY16:BA16"/>
     <mergeCell ref="E34:I34"/>
@@ -14434,6 +15122,7 @@
     <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AP19:AR19"/>
     <mergeCell ref="AJ57:AL57"/>
+    <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
@@ -14443,7 +15132,6 @@
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="AV34:AX34"/>
-    <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
     <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
@@ -14479,13 +15167,13 @@
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
     <mergeCell ref="E44:I44"/>
     <mergeCell ref="BK19:BQ19"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
-    <mergeCell ref="BE58:BG58"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AP27:AR27"/>
     <mergeCell ref="AS28:AU28"/>
@@ -14502,6 +15190,7 @@
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="BE53:BG53"/>
+    <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
@@ -14510,8 +15199,10 @@
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
     <mergeCell ref="Q14:W14"/>
+    <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="Q60:W60"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
@@ -14535,6 +15226,7 @@
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
     <mergeCell ref="AM52:AO52"/>
+    <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="AM39:AO39"/>
@@ -14547,7 +15239,10 @@
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="E60:I60"/>
+    <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
+    <mergeCell ref="X61:AD61"/>
     <mergeCell ref="BK27:BQ27"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="AE29:AF29"/>
@@ -14575,22 +15270,25 @@
     <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="A30:BQ30"/>
-    <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
-    <mergeCell ref="AV58:AX58"/>
     <mergeCell ref="BB20:BD20"/>
     <mergeCell ref="BB14:BD14"/>
     <mergeCell ref="AY24:BA24"/>
     <mergeCell ref="AJ28:AL28"/>
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
+    <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AP46:AR46"/>
+    <mergeCell ref="BK59:BQ59"/>
     <mergeCell ref="BK46:BQ46"/>
     <mergeCell ref="BK40:BQ40"/>
     <mergeCell ref="AE42:AF42"/>
     <mergeCell ref="AS57:AU57"/>
     <mergeCell ref="AY19:BA19"/>
     <mergeCell ref="BK25:BQ25"/>
+    <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="AE44:AF44"/>
@@ -14598,6 +15296,7 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
     <mergeCell ref="AM18:AO18"/>
+    <mergeCell ref="J60:P60"/>
     <mergeCell ref="BK41:BQ41"/>
     <mergeCell ref="BB13:BD13"/>
     <mergeCell ref="AM17:AO17"/>
@@ -14636,7 +15335,7 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="Q6:S6"/>
     <mergeCell ref="BK34:BQ34"/>
-    <mergeCell ref="J58:P58"/>
+    <mergeCell ref="AY59:BA59"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
@@ -14651,6 +15350,7 @@
     <mergeCell ref="AJ29:AL29"/>
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="BK61:BQ61"/>
     <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="BE18:BG18"/>
@@ -14661,7 +15361,8 @@
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
     <mergeCell ref="X19:AD19"/>
-    <mergeCell ref="AS58:AU58"/>
+    <mergeCell ref="AE60:AF60"/>
+    <mergeCell ref="AV59:AX59"/>
     <mergeCell ref="AG34:AI34"/>
     <mergeCell ref="E16:I16"/>
     <mergeCell ref="AV46:AX46"/>
@@ -14671,14 +15372,19 @@
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BE36:BG36"/>
     <mergeCell ref="AE45:AF45"/>
-    <mergeCell ref="X58:AD58"/>
+    <mergeCell ref="AS60:AU60"/>
+    <mergeCell ref="AV61:AX61"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
+    <mergeCell ref="AG59:AI59"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="X60:AD60"/>
+    <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="BB54:BD54"/>
+    <mergeCell ref="AE59:AF59"/>
     <mergeCell ref="AE22:AF22"/>
     <mergeCell ref="BB41:BD41"/>
     <mergeCell ref="J46:P46"/>
@@ -14689,6 +15395,7 @@
     <mergeCell ref="AM20:AO20"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="B19:D19"/>
+    <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J48:P48"/>
@@ -14753,6 +15460,7 @@
     <mergeCell ref="E19:I19"/>
     <mergeCell ref="BE52:BG52"/>
     <mergeCell ref="BB56:BD56"/>
+    <mergeCell ref="AE61:AF61"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AJ32:AL32"/>
@@ -14761,7 +15469,7 @@
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="Q58:W58"/>
+    <mergeCell ref="AY61:BA61"/>
     <mergeCell ref="AV16:AX16"/>
     <mergeCell ref="AJ40:AL40"/>
     <mergeCell ref="AJ27:AL27"/>
@@ -14773,6 +15481,7 @@
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
+    <mergeCell ref="AM59:AO59"/>
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AY43:BA43"/>
@@ -14785,6 +15494,7 @@
     <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="BK60:BQ60"/>
     <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
@@ -14807,10 +15517,10 @@
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="J19:P19"/>
+    <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
-    <mergeCell ref="AG58:AI58"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="AY36:BA36"/>
@@ -14819,13 +15529,13 @@
     <mergeCell ref="X34:AD34"/>
     <mergeCell ref="X28:AD28"/>
     <mergeCell ref="BB47:BD47"/>
+    <mergeCell ref="AG60:AI60"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
     <mergeCell ref="AP33:AR33"/>
     <mergeCell ref="BH41:BJ41"/>
     <mergeCell ref="BE45:BG45"/>
-    <mergeCell ref="AJ58:AL58"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
     <mergeCell ref="BH56:BJ56"/>
@@ -14834,6 +15544,7 @@
     <mergeCell ref="BH31:BJ31"/>
     <mergeCell ref="AJ48:AL48"/>
     <mergeCell ref="AV42:AX42"/>
+    <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="BE46:BG46"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
@@ -14863,6 +15574,7 @@
     <mergeCell ref="BH11:BJ11"/>
     <mergeCell ref="AE19:AF19"/>
     <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AJ59:AL59"/>
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="AJ46:AL46"/>
@@ -14875,6 +15587,7 @@
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
@@ -14900,6 +15613,7 @@
     <mergeCell ref="BH57:BJ57"/>
     <mergeCell ref="AG13:AI13"/>
     <mergeCell ref="AV33:AX33"/>
+    <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="X39:AD39"/>
     <mergeCell ref="AE14:AF14"/>
@@ -14911,11 +15625,13 @@
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E59:I59"/>
     <mergeCell ref="E46:I46"/>
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="J15:P15"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E61:I61"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
@@ -14928,6 +15644,7 @@
     <mergeCell ref="AE27:AF27"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
+    <mergeCell ref="A58:BQ58"/>
     <mergeCell ref="F3:Q3"/>
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
@@ -14976,7 +15693,6 @@
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
     <mergeCell ref="AJ42:AL42"/>
-    <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
     <mergeCell ref="AP52:AR52"/>
@@ -14990,7 +15706,6 @@
     <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="AJ19:AL19"/>
     <mergeCell ref="J56:P56"/>
-    <mergeCell ref="AY58:BA58"/>
     <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
@@ -15002,6 +15717,7 @@
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AM25:AO25"/>
     <mergeCell ref="N6:P6"/>
+    <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
     <mergeCell ref="BE19:BG19"/>
@@ -15024,16 +15740,16 @@
     <mergeCell ref="AG31:AI31"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
-    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE20 AE22:AE29 AE31:AE36 AE38:AE49 AE51:AE57 AE59:AE61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG20 AG22:AG29 AG31:AG36 AG38:AG49 AG51:AG57 AG59:AG61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV20 AV22:AV29 AV31:AV36 AV38:AV49 AV51:AV57 AV59:AV61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
